--- a/Result/checksun_type/面板.xlsx
+++ b/Result/checksun_type/面板.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1643,62 +1643,62 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>50.63500000000001</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>48.54</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>49.6</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>48.54</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2625,62 +2629,62 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>50.225</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>49.41</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>48.53</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>49.41</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>48.53</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3617,52 +3625,52 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>49.675</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>49.26</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>48.5</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>49.26</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4599,12 +4611,12 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -4614,37 +4626,37 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>48.97</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>49.02</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>48.41</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>49.02</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>48.41</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5576,17 +5592,17 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -5596,37 +5612,37 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>48.765</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>48.96</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>48.47</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>48.96</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>48.47</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6558,17 +6578,17 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -6578,37 +6598,37 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>48.745</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>48.63</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>48.63</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7535,62 +7559,62 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>48.795</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>48.64</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>48.8</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>48.64</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8542,37 +8570,37 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>48.625</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>48.45</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>48.94</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>48.45</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>48.94</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9524,37 +9556,37 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>48.58</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>49.15</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10481,62 +10517,62 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10731,11 +10767,15 @@
           <t>35.16</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>32.06</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>28.03</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>32.06</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>28.03</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -10851,7 +10891,7 @@
       </c>
       <c r="DQ11" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR11" t="inlineStr">
@@ -11463,62 +11503,62 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11713,11 +11753,15 @@
           <t>34.055</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>27.74</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>31.36</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>27.74</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -11833,7 +11877,7 @@
       </c>
       <c r="DQ12" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR12" t="inlineStr">
@@ -12445,62 +12489,62 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12695,11 +12739,15 @@
           <t>33.015</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>30.76</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>27.49</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>27.49</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -12815,7 +12863,7 @@
       </c>
       <c r="DQ13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR13" t="inlineStr">
@@ -13427,62 +13475,62 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13677,11 +13725,15 @@
           <t>32.03</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>30.16</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>27.22</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>30.16</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>27.22</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -13797,7 +13849,7 @@
       </c>
       <c r="DQ14" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR14" t="inlineStr">
@@ -14409,62 +14461,62 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14659,11 +14711,15 @@
           <t>31.545</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>27.04</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>27.04</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -14779,7 +14835,7 @@
       </c>
       <c r="DQ15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR15" t="inlineStr">
@@ -15391,62 +15447,62 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15641,11 +15697,15 @@
           <t>31.245</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>29.26</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>26.91</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>29.26</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>26.91</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -15761,7 +15821,7 @@
       </c>
       <c r="DQ16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR16" t="inlineStr">
@@ -16373,62 +16433,62 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16623,11 +16683,15 @@
           <t>30.825</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>26.78</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>26.78</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -16743,7 +16807,7 @@
       </c>
       <c r="DQ17" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR17" t="inlineStr">
@@ -17355,62 +17419,62 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17605,11 +17669,15 @@
           <t>30.12</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>28.25</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>26.6</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>28.25</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>26.6</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -17725,7 +17793,7 @@
       </c>
       <c r="DQ18" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR18" t="inlineStr">
@@ -18342,57 +18410,57 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18587,11 +18655,15 @@
           <t>29.65499999999999</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>27.84</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>26.52</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>27.84</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>26.52</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -18707,7 +18779,7 @@
       </c>
       <c r="DQ19" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR19" t="inlineStr">
